--- a/data/trans_dic/P19F$noche-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,42; 84,41</t>
+          <t>73,55; 84,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,76; 91,17</t>
+          <t>80,95; 90,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,19; 85,69</t>
+          <t>78,51; 85,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,4; 83,2</t>
+          <t>73,71; 82,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,18; 81,29</t>
+          <t>71,54; 81,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,4; 81,06</t>
+          <t>74,22; 80,83</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,78; 83,09</t>
+          <t>74,11; 82,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,8; 85,91</t>
+          <t>77,82; 86,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,59; 83,46</t>
+          <t>77,18; 83,13</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,3; 79,18</t>
+          <t>68,98; 79,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,14; 85,01</t>
+          <t>75,92; 84,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,65; 80,69</t>
+          <t>73,74; 80,61</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,99; 79,57</t>
+          <t>68,76; 80,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,56; 82,09</t>
+          <t>71,62; 82,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,43; 79,38</t>
+          <t>71,47; 79,64</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,16; 89,27</t>
+          <t>77,59; 89,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,85; 86,79</t>
+          <t>75,87; 86,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,96; 86,69</t>
+          <t>78,63; 86,83</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,75; 80,58</t>
+          <t>66,84; 80,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,79; 88,7</t>
+          <t>75,82; 89,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,8; 84,15</t>
+          <t>74,72; 84,45</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>75,56; 79,59</t>
+          <t>75,69; 79,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,87; 82,56</t>
+          <t>78,57; 82,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,76; 80,66</t>
+          <t>77,73; 80,68</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>168174; 193366</t>
+          <t>168483; 193293</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>143963; 162522</t>
+          <t>144311; 161522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>318510; 349036</t>
+          <t>319797; 349955</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>244214; 273086</t>
+          <t>241928; 271598</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>193469; 220940</t>
+          <t>194434; 222339</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>446427; 486374</t>
+          <t>445352; 485025</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>259918; 288822</t>
+          <t>257593; 288197</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>253526; 279962</t>
+          <t>253612; 281079</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>522516; 562091</t>
+          <t>519787; 559874</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>235280; 268834</t>
+          <t>234186; 268305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252047; 281421</t>
+          <t>251331; 280459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>493841; 541030</t>
+          <t>494439; 540520</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>160013; 187246</t>
+          <t>161813; 189599</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>185454; 215741</t>
+          <t>188229; 216794</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>355807; 395421</t>
+          <t>356037; 396736</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>133948; 154963</t>
+          <t>134699; 155273</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>140173; 160400</t>
+          <t>140206; 159866</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>282998; 310714</t>
+          <t>281828; 311183</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83749; 101089</t>
+          <t>83861; 101472</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140550; 166704</t>
+          <t>142485; 167513</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234420; 263728</t>
+          <t>234167; 264674</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1344079; 1415670</t>
+          <t>1346408; 1417911</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1374368; 1438597</t>
+          <t>1369135; 1436644</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2738106; 2840362</t>
+          <t>2737006; 2840885</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$noche-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,55; 84,38</t>
+          <t>73,55; 84,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,95; 90,61</t>
+          <t>80,22; 90,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,51; 85,91</t>
+          <t>78,44; 85,74</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,71; 82,75</t>
+          <t>74,15; 83,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,54; 81,8</t>
+          <t>71,33; 81,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,22; 80,83</t>
+          <t>74,56; 81,19</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,11; 82,91</t>
+          <t>74,31; 82,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,82; 86,25</t>
+          <t>77,58; 85,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,18; 83,13</t>
+          <t>77,44; 83,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,98; 79,03</t>
+          <t>68,95; 79,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,92; 84,72</t>
+          <t>76,16; 84,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,74; 80,61</t>
+          <t>73,79; 80,34</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,76; 80,57</t>
+          <t>68,0; 80,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,62; 82,49</t>
+          <t>70,52; 81,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,47; 79,64</t>
+          <t>72,06; 79,7</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,59; 89,44</t>
+          <t>78,03; 89,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,87; 86,51</t>
+          <t>76,08; 86,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,63; 86,83</t>
+          <t>78,58; 86,6</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,84; 80,88</t>
+          <t>66,71; 81,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,82; 89,13</t>
+          <t>75,83; 89,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,72; 84,45</t>
+          <t>74,33; 83,92</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>75,69; 79,71</t>
+          <t>75,62; 79,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,57; 82,45</t>
+          <t>78,66; 82,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,73; 80,68</t>
+          <t>77,77; 80,66</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>168483; 193293</t>
+          <t>168481; 193901</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>144311; 161522</t>
+          <t>143014; 160917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>319797; 349955</t>
+          <t>319508; 349252</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>241928; 271598</t>
+          <t>243374; 273630</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194434; 222339</t>
+          <t>193881; 222548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>445352; 485025</t>
+          <t>447385; 487151</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>257593; 288197</t>
+          <t>258301; 287880</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>253612; 281079</t>
+          <t>252813; 279598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>519787; 559874</t>
+          <t>521557; 560205</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>234186; 268305</t>
+          <t>234103; 269466</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>251331; 280459</t>
+          <t>252107; 280434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>494439; 540520</t>
+          <t>494811; 538730</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>161813; 189599</t>
+          <t>160026; 188419</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>188229; 216794</t>
+          <t>185341; 214058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>356037; 396736</t>
+          <t>358984; 397021</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>134699; 155273</t>
+          <t>135455; 155049</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>140206; 159866</t>
+          <t>140592; 160689</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>281828; 311183</t>
+          <t>281631; 310361</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83861; 101472</t>
+          <t>83697; 101836</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>142485; 167513</t>
+          <t>142516; 167259</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234167; 264674</t>
+          <t>232961; 263016</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1346408; 1417911</t>
+          <t>1345093; 1415764</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1369135; 1436644</t>
+          <t>1370750; 1440189</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2737006; 2840885</t>
+          <t>2738440; 2840308</t>
         </is>
       </c>
     </row>
